--- a/lite/dist/20261025_Lumentum模型_v0.2.1.xlsx
+++ b/lite/dist/20261025_Lumentum模型_v0.2.1.xlsx
@@ -5645,7 +5645,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5863,7 +5863,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5984,7 +5984,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6105,7 +6105,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6226,7 +6226,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6347,7 +6347,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
